--- a/artfynd/A 54371-2023 artfynd.xlsx
+++ b/artfynd/A 54371-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54371-2023 artfynd.xlsx
+++ b/artfynd/A 54371-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112606798</v>
+        <v>104160249</v>
       </c>
       <c r="B3" t="n">
-        <v>74040</v>
+        <v>73693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798334</v>
+        <v>798851.7842170883</v>
       </c>
       <c r="R3" t="n">
-        <v>7458293</v>
+        <v>7458125.394863522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,14 +865,24 @@
           <t>2022-09-20</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-20</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104160249</v>
+        <v>104160251</v>
       </c>
       <c r="B4" t="n">
-        <v>73693</v>
+        <v>81236</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798851.7842170883</v>
+        <v>799325.73246324</v>
       </c>
       <c r="R4" t="n">
-        <v>7458125.394863522</v>
+        <v>7457907.639483437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,337 +1023,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>112606799</v>
-      </c>
-      <c r="B5" t="n">
-        <v>74040</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Granhult, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>798852</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7458125</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>104160251</v>
-      </c>
-      <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Granhult, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>799325.73246324</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7457907.639483437</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112606801</v>
-      </c>
-      <c r="B7" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Granhult, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>799326</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7457908</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
